--- a/test_doc/new_org/syllabus_6_it.xlsx
+++ b/test_doc/new_org/syllabus_6_it.xlsx
@@ -441,12 +441,12 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Introduction to Computers</t>
+          <t>Fun with Paint</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>Parts of a computer</t>
+          <t>Drawing shapes</t>
         </is>
       </c>
       <c r="C2" t="n">
@@ -461,26 +461,26 @@
     <row r="3">
       <c r="B3" t="inlineStr">
         <is>
-          <t>Uses of computers</t>
+          <t>Colouring pictures</t>
         </is>
       </c>
       <c r="C3" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Operating the Computer</t>
+          <t>Storing Our Work</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Desktop and files</t>
+          <t>Files and folders</t>
         </is>
       </c>
       <c r="C4" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -491,26 +491,26 @@
     <row r="5">
       <c r="B5" t="inlineStr">
         <is>
-          <t>Keyboard and mouse skills</t>
+          <t>Saving and opening</t>
         </is>
       </c>
       <c r="C5" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Word Processing Basics</t>
+          <t>Paint and Drawing Tools</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Creating a document</t>
+          <t>Drawing shapes</t>
         </is>
       </c>
       <c r="C6" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -521,7 +521,7 @@
     <row r="7">
       <c r="B7" t="inlineStr">
         <is>
-          <t>Formatting text</t>
+          <t>Editing pictures</t>
         </is>
       </c>
       <c r="C7" t="n">
@@ -531,12 +531,12 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Paint and Drawing Tools</t>
+          <t>Introduction to Computers</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>Drawing shapes</t>
+          <t>Parts of a computer</t>
         </is>
       </c>
       <c r="C8" t="n">
@@ -551,22 +551,22 @@
     <row r="9">
       <c r="B9" t="inlineStr">
         <is>
-          <t>Editing pictures</t>
+          <t>Uses of computers</t>
         </is>
       </c>
       <c r="C9" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Introduction to the Internet</t>
+          <t>Typing Practice</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>What is the internet</t>
+          <t>Home row practice</t>
         </is>
       </c>
       <c r="C10" t="n">
@@ -574,33 +574,33 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Term 2</t>
+          <t>Term 1</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="B11" t="inlineStr">
         <is>
-          <t>Safe browsing</t>
+          <t>Speed building</t>
         </is>
       </c>
       <c r="C11" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Spreadsheets Basics</t>
+          <t>Presentations</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>Rows, columns and cells</t>
+          <t>Creating slides</t>
         </is>
       </c>
       <c r="C12" t="n">
-        <v>4</v>
+        <v>2</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -611,26 +611,26 @@
     <row r="13">
       <c r="B13" t="inlineStr">
         <is>
-          <t>Simple formulas</t>
+          <t>Presenting ideas</t>
         </is>
       </c>
       <c r="C13" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Presentations</t>
+          <t>Spreadsheets Basics</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>Creating slides</t>
+          <t>Rows, columns and cells</t>
         </is>
       </c>
       <c r="C14" t="n">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -641,7 +641,7 @@
     <row r="15">
       <c r="B15" t="inlineStr">
         <is>
-          <t>Presenting ideas</t>
+          <t>Simple formulas</t>
         </is>
       </c>
       <c r="C15" t="n">
@@ -651,12 +651,12 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Typing Practice</t>
+          <t>Introduction to the Internet</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>Home row practice</t>
+          <t>What is the internet</t>
         </is>
       </c>
       <c r="C16" t="n">
@@ -671,7 +671,7 @@
     <row r="17">
       <c r="B17" t="inlineStr">
         <is>
-          <t>Speed building</t>
+          <t>Safe browsing</t>
         </is>
       </c>
       <c r="C17" t="n">
@@ -690,7 +690,7 @@
         </is>
       </c>
       <c r="C18" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
